--- a/Publication Code/Supplementary Dataset 1.xlsx
+++ b/Publication Code/Supplementary Dataset 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arieknorford/Desktop/Analysis-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84912DF0-4723-B04B-9164-A8A226C0C6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE9DA6A-0A35-084D-98DB-D24D356033DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2320" yWindow="500" windowWidth="26100" windowHeight="16640" xr2:uid="{6E52684B-CCD8-5C44-9E1C-A0D3D20C1701}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6436" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6436" uniqueCount="841">
   <si>
     <t>Mammal</t>
   </si>
@@ -2523,9 +2523,6 @@
   </si>
   <si>
     <t>The plant species dispersed by the mammal species according to the criteria outlined in the manuscript.</t>
-  </si>
-  <si>
-    <t>Native_Introduced.</t>
   </si>
   <si>
     <t>"N" means the species is native to South America. "I" means the species is introduced to South America.</t>
@@ -12796,7 +12793,7 @@
         <v>4.4108108109189201</v>
       </c>
       <c r="L247" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.2">
@@ -28551,10 +28548,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>820</v>
+      </c>
+      <c r="B6" t="s">
         <v>833</v>
-      </c>
-      <c r="B6" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -28562,7 +28559,7 @@
         <v>821</v>
       </c>
       <c r="B7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -28570,7 +28567,7 @@
         <v>822</v>
       </c>
       <c r="B8" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -28578,7 +28575,7 @@
         <v>823</v>
       </c>
       <c r="B9" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -28586,7 +28583,7 @@
         <v>824</v>
       </c>
       <c r="B10" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -28594,7 +28591,7 @@
         <v>825</v>
       </c>
       <c r="B11" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -28602,7 +28599,7 @@
         <v>826</v>
       </c>
       <c r="B12" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
